--- a/reports/ibis_files/hark_lfd2nx_ami_tx/hark_lfd2nx_ami_tx.xlsx
+++ b/reports/ibis_files/hark_lfd2nx_ami_tx/hark_lfd2nx_ami_tx.xlsx
@@ -114,7 +114,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-09T23:35:11-05:00</t>
+          <t>2026-06-12T22:46:19-05:00</t>
         </is>
       </c>
     </row>
@@ -254,7 +254,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7.2.1</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -264,8 +264,10 @@
           <t>Errors</t>
         </is>
       </c>
-      <c r="B16">
-        <v>0</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -274,8 +276,10 @@
           <t>Warnings</t>
         </is>
       </c>
-      <c r="B17">
-        <v>0</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -284,8 +288,10 @@
           <t>Cautions</t>
         </is>
       </c>
-      <c r="B18">
-        <v>0</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -296,7 +302,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C:\Users\simom\Desktop\Projects\IBIS_QA\ibischk721_win_64\ibischk7_64.exe</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -347,7 +353,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -421,14 +427,14 @@
           <t>IBIS file passes IBISCHK</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="D31" t="inlineStr" s="6">
+        <is>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PASS=3. No existing '|IQ Score:' tag found inside the .ibs file. This is reported as a writeback note only; it does not fail the quality check because this tool is intended to help assign the score. | IBISCHK version not found documented inside the .ibs file. This is reported as a documentation note only; it does not block Level 1. | IBISCHK: 0 errors, 0 warning(s): IBISCHK path: C:\Users\simom\Desktop\Projects\IBIS_QA\ibischk721_win_64\ibischk7_64.exe</t>
+          <t>WARN=1, PASS=2. No existing '|IQ Score:' tag found inside the .ibs file. This is reported as a writeback note only; it does not fail the quality check because this tool is intended to help assign the score. | IBISCHK version not found documented inside the .ibs file. This is reported as a documentation note only; it does not block Level 1. | IBISCHK not found on PATH — skipping execution check. Install IBISCHK and ensure it is on PATH</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3655,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2.1-file-lfd2nx_ami_tx.ibs-0d2de14c8a1f</t>
+          <t>2.1-file-lfd2nx_ami_tx.ibs-07c9a9193d18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3716,7 +3722,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2.1-file-lfd2nx_ami_tx.ibs-ee3a71d4188a</t>
+          <t>2.1-file-lfd2nx_ami_tx.ibs-07c9a9193d18-2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3783,7 +3789,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2.1-file-lfd2nx_ami_tx.ibs-31ab159bd8b9</t>
+          <t>2.1-file-lfd2nx_ami_tx.ibs-07c9a9193d18-3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3801,14 +3807,14 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr" s="4">
-        <is>
-          <t>PASS</t>
+      <c r="E4" t="inlineStr" s="6">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="6">
+        <is>
+          <t>WARN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3838,19 +3844,19 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>IBISCHK: 0 errors, 0 warning(s)</t>
+          <t>IBISCHK not found on PATH — skipping execution check. Install IBISCHK and ensure it is on PATH.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>IBISCHK path: C:\Users\simom\Desktop\Projects\IBIS_QA\ibischk721_win_64\ibischk7_64.exe</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3.1.1-component-lfd2nx_Serdes_Tx-57ad47b4bdfb</t>
+          <t>3.1.1-component-lfd2nx_Serdes_Tx-4d8ddb8d7b02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3917,7 +3923,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3.1.2-component-lfd2nx_Serdes_Tx-8742bc888810</t>
+          <t>3.1.2-component-lfd2nx_Serdes_Tx-4009b215b002</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3984,7 +3990,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3.2.1-component-lfd2nx_Serdes_Tx-7fc25f258eb3</t>
+          <t>3.2.1-component-lfd2nx_Serdes_Tx-bb5df55ca552</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4051,7 +4057,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4.1-file-lfd2nx_ami_tx.ibs-e26af11b109b</t>
+          <t>4.1-file-lfd2nx_ami_tx.ibs-915f6a024cde</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4118,7 +4124,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3.2.2-component-lfd2nx_Serdes_Tx-37ea025e6751</t>
+          <t>3.2.2-component-lfd2nx_Serdes_Tx-8a9c85615d65</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4186,7 +4192,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3.3.1-component-lfd2nx_Serdes_Tx-6775f53f966e</t>
+          <t>3.3.1-component-lfd2nx_Serdes_Tx-fc9199787d21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4253,7 +4259,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3.3.2-component-lfd2nx_Serdes_Tx-1249e6014c27</t>
+          <t>3.3.2-component-lfd2nx_Serdes_Tx-f9c0682c71df</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4320,7 +4326,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5.1.1-model-lfd2nx_out-3e8e2d6abe18</t>
+          <t>5.1.1-model-lfd2nx_out-630d1de31009</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4389,7 +4395,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5.2.6-model-lfd2nx_out-da36981056e9</t>
+          <t>5.2.6-model-lfd2nx_out-e333a17a5836</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4456,7 +4462,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5.2.8-model-lfd2nx_out-227ef39b4ea8</t>
+          <t>5.2.8-model-lfd2nx_out-a7f69bdf8a24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4523,7 +4529,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5.5.2-model-lfd2nx_out-1dead530f9cf</t>
+          <t>5.5.2-model-lfd2nx_out-be9172efe38c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4591,7 +4597,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5.1.2-model-lfd2nx_out-dfb2ffe11671</t>
+          <t>5.1.2-model-lfd2nx_out-d148c65dd78d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4658,7 +4664,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5.1.4-model-lfd2nx_out-9475df51f6e2</t>
+          <t>5.1.4-model-lfd2nx_out-948e833febdd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4729,7 +4735,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5.3.6-model-lfd2nx_out-120c5056a0cd</t>
+          <t>5.3.6-model-lfd2nx_out-70aa38987e31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4797,7 +4803,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5.3.14-model-lfd2nx_out-cb9fd77fe5f1</t>
+          <t>5.3.14-model-lfd2nx_out-e686c23982cd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4865,7 +4871,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5.3.10-model-lfd2nx_out-be4310560576</t>
+          <t>5.3.10-model-lfd2nx_out-06f055a01f50</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4932,7 +4938,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5.4.1-model-lfd2nx_out-6861939b6b41</t>
+          <t>5.4.1-model-lfd2nx_out-5bff0c045bf1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4999,7 +5005,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5.4.2-model-lfd2nx_out-704b60b3c5d0</t>
+          <t>5.4.2-model-lfd2nx_out-38b6847f32c1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5066,7 +5072,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5.4.3-model-lfd2nx_out-e992de27a515</t>
+          <t>5.4.3-model-lfd2nx_out-6253a7fb41af</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5133,7 +5139,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5.4.4-model-lfd2nx_out-64bbf0c40ccc</t>
+          <t>5.4.4-model-lfd2nx_out-13db422cacd2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5200,7 +5206,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5.5.4-model-lfd2nx_out-9b6cb049dcb4</t>
+          <t>5.5.4-model-lfd2nx_out-293b5075a37c</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5267,7 +5273,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5.6.2-model-lfd2nx_out-3b2d45a9e7fd</t>
+          <t>5.6.2-model-lfd2nx_out-cc0b0222cc50</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5334,7 +5340,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5.3.1-model-lfd2nx_out-014812c9bc84</t>
+          <t>5.3.1-model-lfd2nx_out-175e2ebce74d</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5401,7 +5407,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5.3.1-model-lfd2nx_out-4d17d3094c9c</t>
+          <t>5.3.1-model-lfd2nx_out-175e2ebce74d-2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5468,7 +5474,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5.3.2-model-lfd2nx_out-c1d373d7793a</t>
+          <t>5.3.2-model-lfd2nx_out-fa8a001efb48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5535,7 +5541,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5.3.3-model-lfd2nx_out-458aaa882980</t>
+          <t>5.3.3-model-lfd2nx_out-6ec6a08eff4c</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5602,7 +5608,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5.3.7-model-lfd2nx_out-5f31d9df95af</t>
+          <t>5.3.7-model-lfd2nx_out-2c36286d0be2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5669,7 +5675,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5.3.7-model-lfd2nx_out-577ef0e1dd20</t>
+          <t>5.3.7-model-lfd2nx_out-2c36286d0be2-2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5736,7 +5742,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5.3.8-model-lfd2nx_out-bc12d99803a5</t>
+          <t>5.3.8-model-lfd2nx_out-09186dadcfc0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5803,7 +5809,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5.3.9-model-lfd2nx_out-7e16d9705862</t>
+          <t>5.3.9-model-lfd2nx_out-30aa5cebf7f2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5870,7 +5876,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5.5.1-model-lfd2nx_out-0d5a751ecd67</t>
+          <t>5.5.1-model-lfd2nx_out-cc182436d880</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5937,7 +5943,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5.5.3-model-lfd2nx_out-adb9677d3def</t>
+          <t>5.5.3-model-lfd2nx_out-3e41c83064f1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6012,6 +6018,73 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>5.9.1-model-lfd2nx_out-0e60171742e1</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5.9.1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>LEVEL 2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr" s="4">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>lfd2nx_out</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Zout worst-case 46.0Ω within 100Ω threshold</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/reports/ibis_files/hark_lfd2nx_ami_tx/hark_lfd2nx_ami_tx.xlsx
+++ b/reports/ibis_files/hark_lfd2nx_ami_tx/hark_lfd2nx_ami_tx.xlsx
@@ -114,7 +114,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-12T22:46:19-05:00</t>
+          <t>2026-06-13T23:04:06-05:00</t>
         </is>
       </c>
     </row>
